--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5331" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="430">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,6 +511,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -700,6 +703,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -710,10 +716,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -726,6 +747,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -733,6 +763,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -740,6 +773,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1259,6 +1295,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1635,7 +1677,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4674,7 +4716,9 @@
       <c r="K30" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4745,10 +4789,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4782,7 +4826,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4804,7 +4848,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4822,7 +4866,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4842,10 +4886,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4879,7 +4923,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4901,7 +4945,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4919,7 +4963,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4939,10 +4983,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4956,7 +5000,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4968,10 +5012,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5022,7 +5066,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5042,10 +5086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5059,7 +5103,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -5068,13 +5112,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5125,7 +5169,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5145,10 +5189,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5246,10 +5290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5265,7 +5309,7 @@
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5278,7 +5322,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5290,7 +5334,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5329,7 +5373,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5349,17 +5393,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5368,7 +5412,7 @@
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5381,7 +5425,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5393,7 +5437,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5432,7 +5476,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5452,17 +5496,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5484,7 +5528,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5496,7 +5540,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5535,7 +5579,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5555,17 +5599,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5587,7 +5631,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5638,7 +5682,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5658,17 +5702,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5677,7 +5721,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5690,7 +5734,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5702,7 +5746,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5741,7 +5785,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5761,10 +5805,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5787,11 +5831,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5842,7 +5886,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5862,10 +5906,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5892,7 +5936,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5943,7 +5987,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5963,17 +6007,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5991,11 +6035,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6046,7 +6090,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6066,17 +6110,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -6094,11 +6138,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6149,7 +6193,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6169,17 +6213,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6197,11 +6241,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6252,7 +6296,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6272,10 +6316,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6289,7 +6333,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6298,16 +6342,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6355,7 +6401,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6375,10 +6421,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6392,7 +6438,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6401,15 +6447,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6458,7 +6506,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6478,10 +6526,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6504,12 +6552,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6557,7 +6609,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6577,10 +6629,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6605,10 +6657,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6636,7 +6692,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6654,7 +6710,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6674,10 +6730,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6700,12 +6756,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6753,7 +6815,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6835,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6799,12 +6861,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6852,7 +6916,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6872,10 +6936,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6898,12 +6962,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6951,7 +7017,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6971,10 +7037,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6988,7 +7054,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6997,7 +7063,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -7038,7 +7104,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -7048,7 +7114,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7068,13 +7134,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -7096,7 +7162,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7149,7 +7215,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7169,10 +7235,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7270,10 +7336,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7371,10 +7437,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7472,10 +7538,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7573,10 +7639,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7676,10 +7742,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7779,10 +7845,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7882,10 +7948,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7985,10 +8051,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8086,10 +8152,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8119,7 +8185,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -8145,7 +8211,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8163,7 +8229,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8183,10 +8249,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8220,7 +8286,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8262,7 +8328,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8282,10 +8348,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8308,7 +8374,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8361,7 +8427,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8381,10 +8447,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8407,7 +8473,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8460,7 +8526,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8480,10 +8546,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8506,7 +8572,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8559,7 +8625,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8579,10 +8645,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8605,7 +8671,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8658,7 +8724,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8678,10 +8744,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8704,7 +8770,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8757,7 +8823,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8777,10 +8843,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8803,10 +8869,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -8858,7 +8924,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8878,10 +8944,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8904,7 +8970,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8957,7 +9023,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8977,10 +9043,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9003,7 +9069,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9056,7 +9122,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9076,10 +9142,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9102,7 +9168,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9155,7 +9221,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9175,13 +9241,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -9203,7 +9269,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9256,7 +9322,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9276,10 +9342,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9377,10 +9443,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9478,10 +9544,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9579,10 +9645,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9680,10 +9746,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9783,10 +9849,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9886,10 +9952,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9989,10 +10055,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10092,10 +10158,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10193,10 +10259,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10226,7 +10292,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10252,7 +10318,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10270,7 +10336,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10290,10 +10356,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10327,7 +10393,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10369,7 +10435,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10389,10 +10455,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10415,7 +10481,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10468,7 +10534,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10488,10 +10554,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10514,7 +10580,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10567,7 +10633,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10587,10 +10653,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10613,10 +10679,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10668,7 +10734,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10688,10 +10754,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10714,7 +10780,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10767,7 +10833,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10787,10 +10853,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10813,7 +10879,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10866,7 +10932,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10886,10 +10952,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10912,7 +10978,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10965,7 +11031,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10985,10 +11051,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11011,7 +11077,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11064,7 +11130,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11084,10 +11150,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11110,7 +11176,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11163,7 +11229,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11183,10 +11249,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11209,7 +11275,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11262,7 +11328,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11282,13 +11348,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>74</v>
@@ -11310,7 +11376,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11363,7 +11429,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11383,10 +11449,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11484,10 +11550,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11585,10 +11651,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11686,10 +11752,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11787,10 +11853,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11890,10 +11956,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11993,10 +12059,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12096,10 +12162,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12199,10 +12265,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12300,10 +12366,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12333,7 +12399,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12359,7 +12425,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12377,7 +12443,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12397,10 +12463,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12434,7 +12500,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12476,7 +12542,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12496,10 +12562,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12522,7 +12588,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12575,7 +12641,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12595,10 +12661,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12621,7 +12687,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12674,7 +12740,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12694,10 +12760,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12720,7 +12786,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12773,7 +12839,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12793,10 +12859,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12819,7 +12885,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12872,7 +12938,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12892,10 +12958,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12918,7 +12984,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12971,7 +13037,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12991,10 +13057,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13017,7 +13083,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13070,7 +13136,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13090,10 +13156,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13116,7 +13182,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13169,7 +13235,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13189,10 +13255,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13215,10 +13281,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -13270,7 +13336,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13290,10 +13356,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13316,7 +13382,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13369,7 +13435,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13389,13 +13455,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>74</v>
@@ -13417,7 +13483,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13470,7 +13536,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13490,10 +13556,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13591,10 +13657,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13692,10 +13758,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13793,10 +13859,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13894,10 +13960,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13997,10 +14063,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14100,10 +14166,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14203,10 +14269,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14306,10 +14372,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14407,10 +14473,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14440,7 +14506,7 @@
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
@@ -14466,7 +14532,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>74</v>
@@ -14484,7 +14550,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14504,10 +14570,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14541,7 +14607,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14583,7 +14649,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14603,10 +14669,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14629,7 +14695,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14682,7 +14748,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14702,10 +14768,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14728,7 +14794,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14781,7 +14847,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14801,10 +14867,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14827,7 +14893,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -14880,7 +14946,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14900,10 +14966,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14926,7 +14992,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14979,7 +15045,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -14999,10 +15065,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15025,7 +15091,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15078,7 +15144,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15098,10 +15164,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15124,7 +15190,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15177,7 +15243,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15197,10 +15263,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15223,7 +15289,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15276,7 +15342,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15296,10 +15362,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15322,10 +15388,10 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -15377,7 +15443,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15397,10 +15463,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15423,7 +15489,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15476,7 +15542,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15496,13 +15562,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>74</v>
@@ -15524,7 +15590,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15577,7 +15643,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15597,10 +15663,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15698,10 +15764,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15799,10 +15865,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15900,10 +15966,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16001,10 +16067,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16104,10 +16170,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16207,10 +16273,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16310,10 +16376,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16413,10 +16479,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16514,10 +16580,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16547,7 +16613,7 @@
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
@@ -16573,7 +16639,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16591,7 +16657,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16611,10 +16677,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16648,7 +16714,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>74</v>
@@ -16690,7 +16756,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16710,10 +16776,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16736,7 +16802,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -16789,7 +16855,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16809,10 +16875,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16835,10 +16901,10 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -16890,7 +16956,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -16910,10 +16976,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -16936,7 +17002,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -16989,7 +17055,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17009,10 +17075,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17035,7 +17101,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17088,7 +17154,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17108,10 +17174,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17134,7 +17200,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17187,7 +17253,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17207,10 +17273,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17233,7 +17299,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17286,7 +17352,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17306,10 +17372,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17332,7 +17398,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17385,7 +17451,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17405,10 +17471,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17431,7 +17497,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17484,7 +17550,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17504,10 +17570,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17530,7 +17596,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17583,7 +17649,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17603,10 +17669,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17629,12 +17695,16 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="L159" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
+      <c r="O159" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>74</v>
       </c>
@@ -17682,7 +17752,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17702,10 +17772,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17803,10 +17873,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17904,10 +17974,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18005,10 +18075,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18106,10 +18176,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18209,10 +18279,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18312,10 +18382,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18415,10 +18485,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18518,10 +18588,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18619,10 +18689,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18649,7 +18719,7 @@
       </c>
       <c r="L169" s="2"/>
       <c r="M169" t="s" s="2">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18658,7 +18728,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>74</v>
@@ -18700,7 +18770,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18720,10 +18790,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18757,7 +18827,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>74</v>
@@ -18799,7 +18869,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -18819,10 +18889,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18845,7 +18915,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -18898,7 +18968,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
